--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -855,7 +855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -918,12 +918,12 @@
     <row r="7" ht="49" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>応募フォームのURLを入れる</t>
+          <t>応募フォームのURL</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>未設定</t>
+          <t>設定済み</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -935,71 +935,88 @@
     <row r="8" ht="49" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>GitHub Pages を有効にする</t>
+          <t>GitHub Pages</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>未設定</t>
+          <t>公開中</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>GitHub → Settings → Pages → Branch に main を指定</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="49" customHeight="1">
+          <t>https://fuku-hiro112.github.io/nenekko-cup/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>応募締切を決めて書く</t>
+          <t>開催日時</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>2026年8月30日（日）20:00</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>index.html の &lt;!-- EDIT: 応募締切 --&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>！ GitHub Pages は当日までに必ず有効にしてください。 当日の更新は 「ファイルを書き換えて push」で反映する仕組みなので、公開していないと 参加者がトーナメント表を見られません。</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+          <t>掲載済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>応募締切</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>2026年8月23日（日）23:59</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>掲載済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>！ 告知の前に、ENTRY のボタンから実際にフォームが開くか一度押して確かめてください。 URL を差し替えたときも同じです。ここが死んでいると応募が1件も来ません。</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>動作確認は次の1行でできます。エラーが出なければ準備完了です。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>python tools/draw_tables.py tools/participants.example.csv</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -15,6 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 飛び入り" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 困ったとき" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 当日チェック" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. スプレッドシートの用意（最初の1回だけ）" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 当日の持ち物チェック" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'はじめに'!$1:$1</definedName>
@@ -24,6 +26,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'3 飛び入り'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'4 困ったとき'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'5 当日チェック'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'6. スプレッドシートの用意（最初の1回だけ）'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'7. 当日の持ち物チェック'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -622,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -760,18 +764,38 @@
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="n"/>
     </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6. スプレッドシートの用意（最初の1回だけ）</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7. 当日の持ち物チェック</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>！ このブックは docs/operation-guide.md から作っています。内容を直すときは Markdown のほうを編集し、python tools/build_operation_xlsx.py を流し直してください。Excel を直接編集しても次の実行で消えます。</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B11:D11"/>
@@ -779,12 +803,149 @@
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>7. 当日の持ち物チェック</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>スプレッドシートに1回戦の卓分けが入っている</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>サイトを開いて、その卓分けが表として出ることを確認した</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>スプレッドシートが「リンクを知っている全員／閲覧者」になっている</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>代わりの人に編集リンクを渡してある（章5）</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Discord のイベントルームと、卓の数だけVCがある（卓1 卓2 …）</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>主催者のDMが開いている（フッターの問い合わせ先になっています）</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>！ 当日にパソコンは要りません。 更新はスプレッドシートの「勝ち」に印を入れるだけで、 git も python も使いません。前日の抽選（章1）だけパソコンで行います。</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1311,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1333,228 +1494,362 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>手順 2-1. 卓分けをサイトに出す</t>
+          <t>手順 2-1. 卓分けをスプレッドシートに貼る</t>
         </is>
       </c>
       <c r="B3" s="20" t="n"/>
       <c r="C3" s="20" t="n"/>
       <c r="D3" s="20" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>python tools/update_bracket.py tournament.json</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>1回戦: 2卓（結果が入っているのは 0卓）
-index.html を更新しました。公開するには commit して push してください。</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>前日に出した卓分けを、スプレッドシートに貼り付けます。列は4つだけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>回戦</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>卓</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>勝ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>1回戦</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>卓1</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>ふろん</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>続けて公開します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>git add -A
-git commit -m "1回戦の卓分け"
-git push</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>数十秒で GitHub Pages に反映されます。参加者はページを開き直すだけです。</t>
-        </is>
-      </c>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>1回戦</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>卓1</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>てるてる</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr"/>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>貼り付けた時点で、サイトを開き直せばもう表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>！ 初回だけ、シートの用意が必要です。 やりかたは章6を見てください。 一度そろえてしまえば、当日は「勝ち」に印を入れるだけになります。</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>手順 2-2. 対局が終わったら結果を書く</t>
+          <t>手順 2-2. 対局が終わったら「勝ち」に印を入れる</t>
         </is>
       </c>
       <c r="B15" s="20" t="n"/>
       <c r="C15" s="20" t="n"/>
       <c r="D15" s="20" t="n"/>
     </row>
-    <row r="17" ht="19" customHeight="1">
+    <row r="17" ht="34" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>tournament.json をテキストエディタで開き、その卓の winners に勝ち上がった人の名前を書きます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="74" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>{
-  "vc": "卓1",
-  "players": ["Fukagami", "アオ", "てるてる", "花園美咲"],
-  "winners": ["Fukagami", "花園美咲"]
-}</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
+          <t>スプレッドシートの「勝ち」の欄に ○ を入れるだけです。 パソコンでもスマホでも、Googleスプレッドシートが開ければ誰でもできます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>回戦</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>卓</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>勝ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>1回戦</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>卓1</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>ふろん</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>・名前は players に書いてあるものをそのままコピーしてください</t>
-        </is>
-      </c>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>1回戦</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>卓1</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>てるてる</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr"/>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>・人数は勝ち抜け数（既定2名）と同じにします</t>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>1回戦</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>卓1</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>アシエンSS</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>・まだ終わっていない卓は [] のままで大丈夫です</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>手順 2-3. 反映する</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>python tools/update_bracket.py tournament.json</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="n"/>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>全卓の結果がそろっていると、次の回戦が自動で組まれます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>1回戦: 2卓（結果が入っているのは 2卓）
-決勝: 1卓（結果が入っているのは 0卓）
-次の回戦を 1 つ組みました（tournament.json に保存済み）。
-index.html を更新しました。公開するには commit して push してください。</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>あとは push するだけです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>git add -A &amp;&amp; git commit -m "1回戦の結果" &amp;&amp; git push</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-    </row>
-    <row r="37" ht="19" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>1回戦</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>卓1</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>どこばか</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr"/>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>勝ちとして扱うもの：○、o、1、TRUE、チェックを入れたチェックボックス、その他の文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>負けとして扱うもの：空欄、×、x、-、0、FALSE、チェックを外したチェックボックス、「なし」「負け」</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>！ チェックボックスを使っても大丈夫です。 外した状態は FALSE という値になりますが、 負けとして扱います。「×」で負けを表しても構いません。</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>・まだ終わっていない卓は空のままにしてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>・2回戦以降の行は書かなくて大丈夫です。 全部の卓に印が入ると、 勝った人を集めて次の回戦が自動で組まれます</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>・メモ用の列を足しても構いません。 見出しの言葉（回戦／卓／参加者／勝ち）で 列を探すので、順番を入れ替えても動きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>手順 2-3. サイトを開き直す</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>2回戦以降も 2-2 → 2-3 の繰り返しです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
+          <t>それだけです。 ページを開くたびにスプレッドシートを読みに行くので、 git も python も要りません。反映まで数十秒かかることがあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>2回戦以降も 2-2 の繰り返しです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>手順 2-4. 決勝</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>決勝の winners には優勝者1名だけ書いてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>{ "vc": "卓1", "players": ["Fukagami", "花園美咲", "ふろん", "アシエンSS"], "winners": ["ふろん"] }</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>決勝の行は自動で作られます。優勝者1名にだけ○を入れてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>！ 見出しが「決勝」の回戦だけ「優勝」が出ます。参加者が4人以下で 1回戦がそのまま決勝になる場合は、シートの「回戦」欄に「決勝」と書いてください。</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>（任意）最終結果をページに焼き付ける</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>大会が終わったあと、スプレッドシートを消しても表が残るようにしたいときだけ、 主催者のパソコンで次を実行します。当日は不要です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>python tools/update_bracket.py tournament.json
+git add -A &amp;&amp; git commit -m "最終結果" &amp;&amp; git push</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A51:D51"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
@@ -1632,7 +1927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1737,95 +2032,195 @@
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>「BRACKET:START / BRACKET:END が見つかりません」</t>
+          <t>表が「当日をお楽しみに」のまま変わらない</t>
         </is>
       </c>
       <c r="B21" s="20" t="n"/>
       <c r="C21" s="20" t="n"/>
       <c r="D21" s="20" t="n"/>
     </row>
-    <row r="23" ht="34" customHeight="1">
+    <row r="23" ht="19" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
+          <t>スプレッドシートが読めていません。上から順に確かめてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>1. index.html の data-sheet にIDが入っているか（章6-3）。空だと何も読みに行きません 2. 共有設定が「リンクを知っている全員」になっているか（章6-2）。 自分だけが見られる状態だと、サイトからは読めません 3. シート名が合っているか。 タブの名前を変えたなら data-sheet-name にも同じ名前を入れます 4. 見出しの行があるか。 1行目は 回戦 / 卓 / 参加者 / 勝ち にしてください 5. 少し待ってから開き直す。反映まで数十秒かかることがあります</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>読めなくてもページの他の部分は普通に動きます。表だけが出ない状態です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>次の回戦が出てこない</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>その回戦のどれか1卓でも「勝ち」が空だと、次には進みません。 全部の卓に印が入っているか確かめてください。わざとそうしてあります（対局中に 先の組み合わせが出てしまわないようにするため）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>負けにしたはずの人が勝ち扱いになる</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>「勝ち」の欄に何を入れているか確かめてください。 空欄・×・0・FALSE・チェックを外したチェックボックスは負けになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>それ以外の文字（△や「？」など）は勝ちとして扱われます。 負けを表す書きかたを増やしたいときは、assets/script.js の NOT_WON に足してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>「決勝」なのに「優勝」と出ない</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>シートの「回戦」欄が「決勝」になっているか確かめてください。 自動で作られた最後の回戦は「決勝」になりますが、手で書いた場合は 「1回戦」のままだと優勝表示になりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>「BRACKET:START / BRACKET:END が見つかりません」</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
           <t>index.html からマーカーのコメントを消してしまっています。 消してしまった場合は BRACKET セクションの中に、次の2行を戻してください。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      &lt;!-- BRACKET:START --&gt;
       &lt;!-- BRACKET:END --&gt;</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>書き換わってほしくないのに上書きされる</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>&lt;!-- BRACKET:START --&gt; 〜 &lt;!-- BRACKET:END --&gt; の間は毎回作り直されます。 手で書いた内容は次の実行で消えます。前後の文章（見出しやリード文）は消えません。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>とりあえず結果だけ見たい</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json --dry</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-    </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="18" t="n"/>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>index.html を書き換えずに、出力される内容だけ確認できます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="29">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
@@ -1838,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1857,95 +2252,260 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B3" s="22" t="inlineStr">
-        <is>
-          <t>参加者.csv と tournament.json が手元にある</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>GitHub Pages が有効になっていて、URLを開ける</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>git push がパスワードを聞かれずに通る（当日つまずきやすい点です）</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>Discord のイベントルームと、卓の数だけVCがある（卓1 卓2 …）</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>主催者のDMが開いている（フッターの問い合わせ先になっています）</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>！ 更新は回戦ごとにまとめてで十分です。対局のたびに更新しようとすると、 司会をしながら数分おきにPC作業をすることになります。</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
+    <row r="3" ht="19" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>当日の更新は、パソコンの操作ができない人でもできます。 スプレッドシートの「勝ち」欄に印を入れるだけだからです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>代わりの人にお願いするときは、次の2つを渡してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>1. スプレッドシートの編集リンク（Googleアカウントがあれば誰でも編集できます） 2. この章と章2の手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>必要ないもの：GitHubアカウント、Python、git、パソコン。スマホだけで足ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>！ サイトを開き直すのは参加者側の操作です。 代わりの人が印を入れたあと、 誰かがページを更新すれば最新の表が出ます。特別な作業は要りません。</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A11:D11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>6. スプレッドシートの用意（最初の1回だけ）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>手順 6-1. シートを作る</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Googleスプレッドシートを新規作成し、1行目に見出しを入れます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>回戦</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>卓</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>勝ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>tools/bracket-sheet.example.csv をインポートすると、この形が入った状態から始められます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>手順 6-2. 「リンクを知っている全員」に共有する</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>右上の「共有」→ 一般的なアクセス →「リンクを知っている全員」→ 閲覧者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>！ 編集者ではなく閲覧者にしてください。 サイトは読むだけなので閲覧権限で足ります。 更新を任せる人には、別途「編集者」として個別に追加してください。</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>手順 6-3. IDをページに書く</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>スプレッドシートのURLはこの形です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/【この部分がID】/edit#gid=0</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>index.html の &lt;!-- EDIT: トーナメント表のスプレッドシートID --&gt; を探し、 data-sheet="..." にそのIDを貼ります。シート名を変えている場合は data-sheet-name="シート1" も埋めてください（既定のままなら空でOK）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>&lt;div class="bracket" data-sheet="1AbCdEf...XyZ" data-sheet-name=""&gt;</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>そのあと commit して push すれば準備完了です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>！ IDが空のあいだは「当日をお楽しみに」が出たままになります。 壊れはしません。</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>仕組みについて</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+    </row>
+    <row r="33" ht="49" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>サイトは Google の公開データ機能（gviz）を使ってシートを読んでいます。 Googleのスプレッドシートは Access-Control-Allow-Origin を返さないため、 ふつうの読み込み方（fetch）では取得できません。 実測して確認したうえで、 制限を受けない JSONP という方式にしてあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>読めなかったとき（未設定・非公開・通信不良・JSが動かない）は、 「当日をお楽しみに」の表示に戻るだけで、ページの他の部分は普通に動きます。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -1472,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="19" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>・2回戦以降の行は書かなくて大丈夫です。 全部の卓に印が入ると、 勝った人を集めて次の回戦が自動で組まれます</t>
+          <t>・2回戦以降の行は書かなくて大丈夫です。 全部の卓に印が入ると、 勝った人を集めて次の回戦が自動で組まれます（下記）</t>
         </is>
       </c>
     </row>
@@ -1747,108 +1747,229 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="13" t="inlineStr"/>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>勝った人を順番に振り分けるので、同じ卓から上がった人どうしが固まりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="46" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>1回戦  卓1 → A, B が勝ち上がり        2回戦  卓1 = A, C, E
+       卓2 → C, D                            卓2 = B, D, F
+       卓3 → E, F                     （出身の卓がばらけます）</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>ただし抽選ではなく決まった順序です。同じ勝ち上がりなら毎回同じ組み合わせになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>手で決めたいときは、シートに「2回戦」の行を書いてください。そちらが優先されます。 自動で組まれるのは「シートに書かれていない先の回戦」だけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>回戦</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>卓</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>勝ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>1回戦</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>卓1</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>ふろん</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr"/>
+      <c r="C47" s="16" t="inlineStr"/>
+      <c r="D47" s="16" t="inlineStr"/>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>2回戦</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>卓1</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>ふろん</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr"/>
+    </row>
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>当日「この2人は同じ卓を避けたい」といった調整が要るときに使えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>手順 2-3. サイトを開き直す</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n"/>
-      <c r="C35" s="20" t="n"/>
-      <c r="D35" s="20" t="n"/>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>それだけです。 ページを開くたびにスプレッドシートを読みに行くので、 git も python も要りません。反映まで数十秒かかることがあります。</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>2回戦以降も 2-2 の繰り返しです。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>手順 2-4. 決勝</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n"/>
-      <c r="C41" s="20" t="n"/>
-      <c r="D41" s="20" t="n"/>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="20" t="n"/>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>決勝の行は自動で作られます。優勝者1名にだけ○を入れてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>！ 見出しが「決勝」の回戦だけ「優勝」が出ます。参加者が4人以下で 1回戦がそのまま決勝になる場合は、シートの「回戦」欄に「決勝」と書いてください。</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-    </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="19" t="inlineStr">
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>（任意）最終結果をページに焼き付ける</t>
         </is>
       </c>
-      <c r="B47" s="20" t="n"/>
-      <c r="C47" s="20" t="n"/>
-      <c r="D47" s="20" t="n"/>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="B64" s="20" t="n"/>
+      <c r="C64" s="20" t="n"/>
+      <c r="D64" s="20" t="n"/>
+    </row>
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>大会が終わったあと、スプレッドシートを消しても表が残るようにしたいときだけ、 主催者のパソコンで次を実行します。当日は不要です。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json
 git add -A &amp;&amp; git commit -m "最終結果" &amp;&amp; git push</t>
         </is>
       </c>
-      <c r="B51" s="18" t="n"/>
-      <c r="C51" s="18" t="n"/>
-      <c r="D51" s="18" t="n"/>
+      <c r="B68" s="18" t="n"/>
+      <c r="C68" s="18" t="n"/>
+      <c r="D68" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="28">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A68:D68"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A58:D58"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A64:D64"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A66:D66"/>
     <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -1472,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1750,226 +1750,162 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="13" t="inlineStr"/>
     </row>
-    <row r="37" ht="19" customHeight="1">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>勝った人を順番に振り分けるので、同じ卓から上がった人どうしが固まりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="46" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+          <t>章6でスクリプトを入れておくと、その回戦の全部の卓に印が入った瞬間、 次の回戦の行がシートに追加されます（薄い黄色で色が付きます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>追加された行の「勝ち」に、また印を入れてください。これを決勝まで繰り返すだけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>勝った人は順番に振り分けるので、同じ卓から上がった人どうしが固まりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="46" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>1回戦  卓1 → A, B が勝ち上がり        2回戦  卓1 = A, C, E
        卓2 → C, D                            卓2 = B, D, F
        卓3 → E, F                     （出身の卓がばらけます）</t>
         </is>
       </c>
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="18" t="n"/>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>ただし抽選ではなく決まった順序です。同じ勝ち上がりなら毎回同じ組み合わせになります。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>手で決めたいときは、シートに「2回戦」の行を書いてください。そちらが優先されます。 自動で組まれるのは「シートに書かれていない先の回戦」だけです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>回戦</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>卓</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>参加者</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>勝ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>1回戦</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>卓1</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>ふろん</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr"/>
-      <c r="C47" s="16" t="inlineStr"/>
-      <c r="D47" s="16" t="inlineStr"/>
-    </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>2回戦</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>卓1</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>ふろん</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr"/>
-    </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>当日「この2人は同じ卓を避けたい」といった調整が要るときに使えます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>組み合わせを手で決めたいときは、追加された行を書き換えてかまいません。 一度作られた行が勝手に作り直されることはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>手順 2-3. サイトを開き直す</t>
         </is>
       </c>
-      <c r="B52" s="20" t="n"/>
-      <c r="C52" s="20" t="n"/>
-      <c r="D52" s="20" t="n"/>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>それだけです。 ページを開くたびにスプレッドシートを読みに行くので、 git も python も要りません。反映まで数十秒かかることがあります。</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>2回戦以降も 2-2 の繰り返しです。</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="19" t="inlineStr">
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>手順 2-4. 決勝</t>
         </is>
       </c>
-      <c r="B58" s="20" t="n"/>
-      <c r="C58" s="20" t="n"/>
-      <c r="D58" s="20" t="n"/>
-    </row>
-    <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>決勝の行は自動で作られます。優勝者1名にだけ○を入れてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="34" customHeight="1">
-      <c r="A62" s="14" t="inlineStr">
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>！ 見出しが「決勝」の回戦だけ「優勝」が出ます。参加者が4人以下で 1回戦がそのまま決勝になる場合は、シートの「回戦」欄に「決勝」と書いてください。</t>
         </is>
       </c>
-      <c r="B62" s="10" t="n"/>
-      <c r="C62" s="10" t="n"/>
-      <c r="D62" s="10" t="n"/>
-    </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="19" t="inlineStr">
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>（任意）最終結果をページに焼き付ける</t>
         </is>
       </c>
-      <c r="B64" s="20" t="n"/>
-      <c r="C64" s="20" t="n"/>
-      <c r="D64" s="20" t="n"/>
-    </row>
-    <row r="66" ht="34" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>大会が終わったあと、スプレッドシートを消しても表が残るようにしたいときだけ、 主催者のパソコンで次を実行します。当日は不要です。</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="17" t="inlineStr">
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json
 git add -A &amp;&amp; git commit -m "最終結果" &amp;&amp; git push</t>
         </is>
       </c>
-      <c r="B68" s="18" t="n"/>
-      <c r="C68" s="18" t="n"/>
-      <c r="D68" s="18" t="n"/>
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A68:D68"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A58:D58"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A51:D51"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A66:D66"/>
     <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2048,7 +1984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2225,7 +2161,7 @@
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>「決勝」なのに「優勝」と出ない</t>
+          <t>次の回戦の行がシートに増えない</t>
         </is>
       </c>
       <c r="B39" s="20" t="n"/>
@@ -2235,84 +2171,122 @@
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
+          <t>章6-3のスクリプトが入っていないか、承認がまだです。 「勝ち」の欄を編集したときに動くので、他の列を触っても増えません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>・拡張機能 → Apps Script を開き、コードが貼られているか確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>・「勝ち」の欄に何か入れ直して、許可を求められたら承認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>・それでも増えないときは、その回戦に印が入っていない卓が残っていないか確かめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>「決勝」なのに「優勝」と出ない</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
           <t>シートの「回戦」欄が「決勝」になっているか確かめてください。 自動で作られた最後の回戦は「決勝」になりますが、手で書いた場合は 「1回戦」のままだと優勝表示になりません。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>「BRACKET:START / BRACKET:END が見つかりません」</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n"/>
-      <c r="C43" s="20" t="n"/>
-      <c r="D43" s="20" t="n"/>
-    </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>index.html からマーカーのコメントを消してしまっています。 消してしまった場合は BRACKET セクションの中に、次の2行を戻してください。</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      &lt;!-- BRACKET:START --&gt;
       &lt;!-- BRACKET:END --&gt;</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="n"/>
-      <c r="C47" s="18" t="n"/>
-      <c r="D47" s="18" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>書き換わってほしくないのに上書きされる</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>&lt;!-- BRACKET:START --&gt; 〜 &lt;!-- BRACKET:END --&gt; の間は毎回作り直されます。 手で書いた内容は次の実行で消えます。前後の文章（見出しやリード文）は消えません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="19" t="inlineStr">
-        <is>
-          <t>とりあえず結果だけ見たい</t>
-        </is>
-      </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>python tools/update_bracket.py tournament.json --dry</t>
         </is>
       </c>
       <c r="B55" s="18" t="n"/>
       <c r="C55" s="18" t="n"/>
       <c r="D55" s="18" t="n"/>
     </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>書き換わってほしくないのに上書きされる</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>&lt;!-- BRACKET:START --&gt; 〜 &lt;!-- BRACKET:END --&gt; の間は毎回作り直されます。 手で書いた内容は次の実行で消えます。前後の文章（見出しやリード文）は消えません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>とりあえず結果だけ見たい</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>python tools/update_bracket.py tournament.json --dry</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="n"/>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+    </row>
+    <row r="65" ht="19" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>index.html を書き換えずに、出力される内容だけ確認できます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="34">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
@@ -2321,18 +2295,23 @@
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A44:D44"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A49:D49"/>
     <mergeCell ref="A51:D51"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A27:D27"/>
@@ -2431,7 +2410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2526,107 +2505,153 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>手順 6-3. IDをページに書く</t>
+          <t>手順 6-3. 次の回戦を自動で作るスクリプトを入れる</t>
         </is>
       </c>
       <c r="B17" s="20" t="n"/>
       <c r="C17" s="20" t="n"/>
       <c r="D17" s="20" t="n"/>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>これを入れると、2回戦以降の行をシートが自分で増やします。 入れないと、 表には次の回戦が出るものの、勝ちを書き込む行がシートに無い状態になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="49" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>1. スプレッドシートを開く 2. 上のメニューから 拡張機能 → Apps Script 3. 出てきたコードを全部消して、tools/bracket.gs の中身を貼り付ける 4. 保存（フロッピーのアイコン） 5. シートに戻って「勝ち」の欄に何か入れてみる → 初回だけ許可を求められます。 自分のアカウントで承認してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>これで、その回戦の全部の卓に印が入った瞬間、次の回戦の行が追加されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>！ メニューではなく「編集したとき」に動かしています。 スプレッドシートの スマホアプリではカスタムメニューが出ないため、メニュー方式だと 代わりの人がスマホだけのときに使えないからです。</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>手順 6-4. IDをページに書く</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>スプレッドシートのURLはこの形です。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/【この部分がID】/edit#gid=0</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>index.html の &lt;!-- EDIT: トーナメント表のスプレッドシートID --&gt; を探し、 data-sheet="..." にそのIDを貼ります。シート名を変えている場合は data-sheet-name="シート1" も埋めてください（既定のままなら空でOK）。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>&lt;div class="bracket" data-sheet="1AbCdEf...XyZ" data-sheet-name=""&gt;</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-    </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>そのあと commit して push すれば準備完了です。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>！ IDが空のあいだは「当日をお楽しみに」が出たままになります。 壊れはしません。</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>仕組みについて</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-    </row>
-    <row r="33" ht="49" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+    </row>
+    <row r="43" ht="49" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>サイトは Google の公開データ機能（gviz）を使ってシートを読んでいます。 Googleのスプレッドシートは Access-Control-Allow-Origin を返さないため、 ふつうの読み込み方（fetch）では取得できません。 実測して確認したうえで、 制限を受けない JSONP という方式にしてあります。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>読めなかったとき（未設定・非公開・通信不良・JSが動かない）は、 「当日をお楽しみに」の表示に戻るだけで、ページの他の部分は普通に動きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="22">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -1472,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1753,131 +1753,152 @@
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>章6でスクリプトを入れておくと、その回戦の全部の卓に印が入った瞬間、 次の回戦の行がシートに追加されます（薄い黄色で色が付きます）。</t>
+          <t>章6でスクリプトを入れておくと、条件がそろった瞬間に 次の回戦の行がシートに追加されます（薄い黄色で色が付きます）。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
+          <t>行が増える条件（いちばん下の回戦について、すべて満たしたとき）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>1. 卓が2つ以上ある（1つなら決勝とみなして終わります） 2. すべての卓に勝ちの印が付いている 3. 卓ごとの勝ちの数がそろっている（卓1が2人なら、卓2も卓3も2人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>3つ目があるので、1人ずつ入れている途中で組まれることはありません。 最後の1つを入れた瞬間にまとめて作られます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
           <t>追加された行の「勝ち」に、また印を入れてください。これを決勝まで繰り返すだけです。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>勝った人は順番に振り分けるので、同じ卓から上がった人どうしが固まりません。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="46" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>1回戦  卓1 → A, B が勝ち上がり        2回戦  卓1 = A, C, E
        卓2 → C, D                            卓2 = B, D, F
        卓3 → E, F                     （出身の卓がばらけます）</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>ただし抽選ではなく決まった順序です。同じ勝ち上がりなら毎回同じ組み合わせになります。</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>組み合わせを手で決めたいときは、追加された行を書き換えてかまいません。 一度作られた行が勝手に作り直されることはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>手順 2-3. サイトを開き直す</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>それだけです。 ページを開くたびにスプレッドシートを読みに行くので、 git も python も要りません。反映まで数十秒かかることがあります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>2回戦以降も 2-2 の繰り返しです。</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>手順 2-4. 決勝</t>
+          <t>手順 2-3. サイトを開き直す</t>
         </is>
       </c>
       <c r="B55" s="20" t="n"/>
       <c r="C55" s="20" t="n"/>
       <c r="D55" s="20" t="n"/>
     </row>
-    <row r="57" ht="19" customHeight="1">
+    <row r="57" ht="34" customHeight="1">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>決勝の行は自動で作られます。優勝者1名にだけ○を入れてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>！ 見出しが「決勝」の回戦だけ「優勝」が出ます。参加者が4人以下で 1回戦がそのまま決勝になる場合は、シートの「回戦」欄に「決勝」と書いてください。</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="n"/>
-      <c r="C59" s="10" t="n"/>
-      <c r="D59" s="10" t="n"/>
+          <t>それだけです。 ページを開くたびにスプレッドシートを読みに行くので、 git も python も要りません。反映まで数十秒かかることがあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>2回戦以降も 2-2 の繰り返しです。</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>（任意）最終結果をページに焼き付ける</t>
+          <t>手順 2-4. 決勝</t>
         </is>
       </c>
       <c r="B61" s="20" t="n"/>
       <c r="C61" s="20" t="n"/>
       <c r="D61" s="20" t="n"/>
     </row>
-    <row r="63" ht="34" customHeight="1">
+    <row r="63" ht="19" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
         <is>
+          <t>決勝の行は自動で作られます。優勝者1名にだけ○を入れてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>！ 見出しが「決勝」の回戦だけ「優勝」が出ます。参加者が4人以下で 1回戦がそのまま決勝になる場合は、シートの「回戦」欄に「決勝」と書いてください。</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="10" t="n"/>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>（任意）最終結果をページに焼き付ける</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
           <t>大会が終わったあと、スプレッドシートを消しても表が残るようにしたいときだけ、 主催者のパソコンで次を実行します。当日は不要です。</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json
 git add -A &amp;&amp; git commit -m "最終結果" &amp;&amp; git push</t>
         </is>
       </c>
-      <c r="B65" s="18" t="n"/>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
+      <c r="B71" s="18" t="n"/>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="32">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A53:D53"/>
@@ -1886,6 +1907,7 @@
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A67:D67"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
@@ -1896,6 +1918,7 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A69:D69"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A65:D65"/>
     <mergeCell ref="A41:D41"/>
@@ -1905,6 +1928,7 @@
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A71:D71"/>
     <mergeCell ref="A47:D47"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
@@ -1984,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2192,135 +2216,143 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>・それでも増えないときは、その回戦に印が入っていない卓が残っていないか確かめる</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="19" t="inlineStr">
+          <t>・その回戦に印が入っていない卓が残っていないか確かめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>・卓ごとの勝ちの数がそろっているか確かめる。卓1が2人で卓2が1人だと、 まだ入力の途中とみなして待ちます</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>「決勝」なのに「優勝」と出ない</t>
         </is>
       </c>
-      <c r="B47" s="20" t="n"/>
-      <c r="C47" s="20" t="n"/>
-      <c r="D47" s="20" t="n"/>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="20" t="n"/>
+      <c r="D48" s="20" t="n"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>シートの「回戦」欄が「決勝」になっているか確かめてください。 自動で作られた最後の回戦は「決勝」になりますが、手で書いた場合は 「1回戦」のままだと優勝表示になりません。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>「BRACKET:START / BRACKET:END が見つかりません」</t>
         </is>
       </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>index.html からマーカーのコメントを消してしまっています。 消してしまった場合は BRACKET セクションの中に、次の2行を戻してください。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      &lt;!-- BRACKET:START --&gt;
       &lt;!-- BRACKET:END --&gt;</t>
         </is>
       </c>
-      <c r="B55" s="18" t="n"/>
-      <c r="C55" s="18" t="n"/>
-      <c r="D55" s="18" t="n"/>
-    </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="19" t="inlineStr">
+      <c r="B56" s="18" t="n"/>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>書き換わってほしくないのに上書きされる</t>
         </is>
       </c>
-      <c r="B57" s="20" t="n"/>
-      <c r="C57" s="20" t="n"/>
-      <c r="D57" s="20" t="n"/>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="20" t="n"/>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>&lt;!-- BRACKET:START --&gt; 〜 &lt;!-- BRACKET:END --&gt; の間は毎回作り直されます。 手で書いた内容は次の実行で消えます。前後の文章（見出しやリード文）は消えません。</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>とりあえず結果だけ見たい</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n"/>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="B62" s="20" t="n"/>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="20" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json --dry</t>
         </is>
       </c>
-      <c r="B63" s="18" t="n"/>
-      <c r="C63" s="18" t="n"/>
-      <c r="D63" s="18" t="n"/>
-    </row>
-    <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+    </row>
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>index.html を書き換えずに、出力される内容だけ確認できます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="35">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A64:D64"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A66:D66"/>
     <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -1472,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1736,7 +1736,7 @@
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>・2回戦以降の行は書かなくて大丈夫です。 全部の卓に印が入ると、 勝った人を集めて次の回戦が自動で組まれます（下記）</t>
+          <t>・2回戦以降の行は手で書かなくて大丈夫です。 全部の卓に印を入れたあと、 「次の回戦を作る」を押せば組まれます（下記）</t>
         </is>
       </c>
     </row>
@@ -1753,183 +1753,274 @@
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>章6でスクリプトを入れておくと、条件がそろった瞬間に 次の回戦の行がシートに追加されます（薄い黄色で色が付きます）。</t>
+          <t>その回戦の勝ちを入れ終わったら、「次の回戦を作る」を押してください。 次の回戦の行がシートに追加されます（薄い黄色で色が付きます）。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>行が増える条件（いちばん下の回戦について、すべて満たしたとき）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>1. 卓が2つ以上ある（1つなら決勝とみなして終わります） 2. すべての卓に勝ちの印が付いている 3. 卓ごとの勝ちの数がそろっている（卓1が2人なら、卓2も卓3も2人）</t>
+          <t>押しかたは3つあります。どれも同じことをします（章6-3で用意します）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="15" t="inlineStr"/>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>押しかた</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>使える場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>メニューの「ポカジャン大会 → 次の回戦を作る」</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>パソコン</t>
         </is>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>3つ目があるので、1人ずつ入れている途中で組まれることはありません。 最後の1つを入れた瞬間にまとめて作られます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>シートに置いた図形ボタン</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>パソコン</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>「実行」列のチェックボックス</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>スマホでも押せます</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>勝手には増えません。 押したときだけ動くので、入力の途中で組まれる心配はありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>作れないときは、画面の右下に理由が出ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>1回戦の勝ちの数がそろっていません（卓1は2人・卓2は2人・卓3は1人）。入れ忘れがないか確かめてください。</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="18" t="n"/>
+      <c r="D50" s="18" t="n"/>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>作れる条件は、いちばん下の回戦について次の3つです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>1. 卓が2つ以上ある（1つなら、それが最後の卓です） 2. すべての卓に勝ちの印が付いている 3. 卓ごとの勝ちの数がそろっている（卓1が2人なら、卓2も卓3も2人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>追加された行の「勝ち」に、また印を入れてください。これを決勝まで繰り返すだけです。</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>勝った人は順番に振り分けるので、同じ卓から上がった人どうしが固まりません。</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="46" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
+    <row r="60" ht="46" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>1回戦  卓1 → A, B が勝ち上がり        2回戦  卓1 = A, C, E
        卓2 → C, D                            卓2 = B, D, F
        卓3 → E, F                     （出身の卓がばらけます）</t>
         </is>
       </c>
-      <c r="B49" s="18" t="n"/>
-      <c r="C49" s="18" t="n"/>
-      <c r="D49" s="18" t="n"/>
-    </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+    </row>
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>ただし抽選ではなく決まった順序です。同じ勝ち上がりなら毎回同じ組み合わせになります。</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>組み合わせを手で決めたいときは、追加された行を書き換えてかまいません。 一度作られた行が勝手に作り直されることはありません。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>手順 2-3. サイトを開き直す</t>
         </is>
       </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="B66" s="20" t="n"/>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="20" t="n"/>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>それだけです。 ページを開くたびにスプレッドシートを読みに行くので、 git も python も要りません。反映まで数十秒かかることがあります。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="19" customHeight="1">
-      <c r="A59" s="12" t="inlineStr">
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>2回戦以降も 2-2 の繰り返しです。</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>手順 2-4. 決勝</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n"/>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-    </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>決勝の行は自動で作られます。優勝者1名にだけ○を入れてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="B72" s="20" t="n"/>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="20" t="n"/>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>残りが4人以下になると、「次の回戦を作る」を押したときに決勝の行ができます。 優勝者1名にだけ○を入れてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="A76" s="14" t="inlineStr">
         <is>
           <t>！ 見出しが「決勝」の回戦だけ「優勝」が出ます。参加者が4人以下で 1回戦がそのまま決勝になる場合は、シートの「回戦」欄に「決勝」と書いてください。</t>
         </is>
       </c>
-      <c r="B65" s="10" t="n"/>
-      <c r="C65" s="10" t="n"/>
-      <c r="D65" s="10" t="n"/>
-    </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="19" t="inlineStr">
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>（任意）最終結果をページに焼き付ける</t>
         </is>
       </c>
-      <c r="B67" s="20" t="n"/>
-      <c r="C67" s="20" t="n"/>
-      <c r="D67" s="20" t="n"/>
-    </row>
-    <row r="69" ht="34" customHeight="1">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="20" t="n"/>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t>大会が終わったあと、スプレッドシートを消しても表が残るようにしたいときだけ、 主催者のパソコンで次を実行します。当日は不要です。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json
 git add -A &amp;&amp; git commit -m "最終結果" &amp;&amp; git push</t>
         </is>
       </c>
-      <c r="B71" s="18" t="n"/>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
+      <c r="B82" s="18" t="n"/>
+      <c r="C82" s="18" t="n"/>
+      <c r="D82" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="35">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A82:D82"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A80:D80"/>
     <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A76:D76"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2008,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2185,132 +2276,195 @@
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>次の回戦の行がシートに増えない</t>
+          <t>「次の回戦を作る」を押しても増えない</t>
         </is>
       </c>
       <c r="B39" s="20" t="n"/>
       <c r="C39" s="20" t="n"/>
       <c r="D39" s="20" t="n"/>
     </row>
-    <row r="41" ht="34" customHeight="1">
+    <row r="41" ht="19" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>章6-3のスクリプトが入っていないか、承認がまだです。 「勝ち」の欄を編集したときに動くので、他の列を触っても増えません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>・拡張機能 → Apps Script を開き、コードが貼られているか確認する</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>・「勝ち」の欄に何か入れ直して、許可を求められたら承認する</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>・その回戦に印が入っていない卓が残っていないか確かめる</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>・卓ごとの勝ちの数がそろっているか確かめる。卓1が2人で卓2が1人だと、 まだ入力の途中とみなして待ちます</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="19" t="inlineStr">
+          <t>押すと、画面の右下に理由が出ます。 まずそれを読んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>出る文</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>どうするか</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>「〜に、まだ勝ちの印がありません」</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>その卓の勝ちを入れてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>「勝ちの数がそろっていません（卓1は2人・卓2は1人…）」</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>入れ忘れです。数をそろえてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>「〜は1卓だけなので、これが最後です」</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>もう決勝まで来ています。正常です</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>「シートの見出しが読めません」</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>1行目を「回戦 / 卓 / 参加者 / 勝ち」にしてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>何も出ない場合は、スクリプトが入っていないか承認がまだです。 拡張機能 → Apps Script を開き、コードが貼られているか確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>メニューやボタンが出ない</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>スマホのアプリでは、メニューも図形ボタンも表示されません。 「実行」列のチェックボックス（章6-3）を使ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>パソコンでメニューが出ないときは、スプレッドシートを開き直してください。 メニューはシートを開いたときに作られます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>「決勝」なのに「優勝」と出ない</t>
         </is>
       </c>
-      <c r="B48" s="20" t="n"/>
-      <c r="C48" s="20" t="n"/>
-      <c r="D48" s="20" t="n"/>
-    </row>
-    <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>シートの「回戦」欄が「決勝」になっているか確かめてください。 自動で作られた最後の回戦は「決勝」になりますが、手で書いた場合は 「1回戦」のままだと優勝表示になりません。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>「BRACKET:START / BRACKET:END が見つかりません」</t>
         </is>
       </c>
-      <c r="B52" s="20" t="n"/>
-      <c r="C52" s="20" t="n"/>
-      <c r="D52" s="20" t="n"/>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>index.html からマーカーのコメントを消してしまっています。 消してしまった場合は BRACKET セクションの中に、次の2行を戻してください。</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      &lt;!-- BRACKET:START --&gt;
       &lt;!-- BRACKET:END --&gt;</t>
         </is>
       </c>
-      <c r="B56" s="18" t="n"/>
-      <c r="C56" s="18" t="n"/>
-      <c r="D56" s="18" t="n"/>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="19" t="inlineStr">
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>書き換わってほしくないのに上書きされる</t>
         </is>
       </c>
-      <c r="B58" s="20" t="n"/>
-      <c r="C58" s="20" t="n"/>
-      <c r="D58" s="20" t="n"/>
-    </row>
-    <row r="60" ht="34" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>&lt;!-- BRACKET:START --&gt; 〜 &lt;!-- BRACKET:END --&gt; の間は毎回作り直されます。 手で書いた内容は次の実行で消えます。前後の文章（見出しやリード文）は消えません。</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="19" t="inlineStr">
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>とりあえず結果だけ見たい</t>
         </is>
       </c>
-      <c r="B62" s="20" t="n"/>
-      <c r="C62" s="20" t="n"/>
-      <c r="D62" s="20" t="n"/>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json --dry</t>
         </is>
       </c>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-    </row>
-    <row r="66" ht="19" customHeight="1">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="B73" s="18" t="n"/>
+      <c r="C73" s="18" t="n"/>
+      <c r="D73" s="18" t="n"/>
+    </row>
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>index.html を書き換えずに、出力される内容だけ確認できます。</t>
         </is>
@@ -2321,38 +2475,38 @@
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A44:D44"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A67:D67"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A73:D73"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A51:D51"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A69:D69"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A66:D66"/>
     <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A75:D75"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A71:D71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
@@ -2442,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2537,7 +2691,7 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>手順 6-3. 次の回戦を自動で作るスクリプトを入れる</t>
+          <t>手順 6-3. 「次の回戦を作る」を押せるようにする</t>
         </is>
       </c>
       <c r="B17" s="20" t="n"/>
@@ -2547,124 +2701,159 @@
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>これを入れると、2回戦以降の行をシートが自分で増やします。 入れないと、 表には次の回戦が出るものの、勝ちを書き込む行がシートに無い状態になります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="49" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>1. スプレッドシートを開く 2. 上のメニューから 拡張機能 → Apps Script 3. 出てきたコードを全部消して、tools/bracket.gs の中身を貼り付ける 4. 保存（フロッピーのアイコン） 5. シートに戻って「勝ち」の欄に何か入れてみる → 初回だけ許可を求められます。 自分のアカウントで承認してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>これで、その回戦の全部の卓に印が入った瞬間、次の回戦の行が追加されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>！ メニューではなく「編集したとき」に動かしています。 スプレッドシートの スマホアプリではカスタムメニューが出ないため、メニュー方式だと 代わりの人がスマホだけのときに使えないからです。</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+          <t>これを入れると、2回戦以降の行を作れるようになります。 入れないと、 表には次の回戦が出るものの、勝ちを書き込む行がシートに無い状態になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>まずスクリプトを入れます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>1. スプレッドシートを開く 2. 上のメニューから 拡張機能 → Apps Script 3. 出てきたコードを全部消して、tools/bracket.gs の中身を貼り付ける 4. 保存（フロッピーのアイコン） 5. スプレッドシートを開き直す → 上に 「ポカジャン大会」というメニューが増えます 6. 「ポカジャン大会 → 次の回戦を作る」を一度押す → 初回だけ許可を求められます。 自分のアカウントで承認してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>メニューだけで足りるならここまでで完了です。 押しやすくしたい場合は、 次のどちらかを足してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>1. 挿入 → 図形描画 → 四角を描いて「次の回戦を作る」と書く → 保存して閉じる 2. 置かれた図形の右上の 「⋮」→ スクリプトを割り当て 3. createNextRound と入力して OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>以後、その図形を押すだけで動きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="13" t="inlineStr"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>1. 空いている列の1行目に「実行」と書く 2. その下のセルを選んで、挿入 → チェックボックス 3. チェックを入れると走り、自動でチェックが外れます</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>！ スマホのアプリでは、メニューも図形ボタンも出ません。 代わりの人がスマホだけで進める可能性があるなら、 チェックボックスを必ず用意しておいてください。</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>手順 6-4. IDをページに書く</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>スプレッドシートのURLはこの形です。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/【この部分がID】/edit#gid=0</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>index.html の &lt;!-- EDIT: トーナメント表のスプレッドシートID --&gt; を探し、 data-sheet="..." にそのIDを貼ります。シート名を変えている場合は data-sheet-name="シート1" も埋めてください（既定のままなら空でOK）。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>&lt;div class="bracket" data-sheet="1AbCdEf...XyZ" data-sheet-name=""&gt;</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>そのあと commit して push すれば準備完了です。</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>！ IDが空のあいだは「当日をお楽しみに」が出たままになります。 壊れはしません。</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>仕組みについて</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n"/>
-      <c r="C41" s="20" t="n"/>
-      <c r="D41" s="20" t="n"/>
-    </row>
-    <row r="43" ht="49" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+    </row>
+    <row r="55" ht="49" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>サイトは Google の公開データ機能（gviz）を使ってシートを読んでいます。 Googleのスプレッドシートは Access-Control-Allow-Origin を返さないため、 ふつうの読み込み方（fetch）では取得できません。 実測して確認したうえで、 制限を受けない JSONP という方式にしてあります。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>読めなかったとき（未設定・非公開・通信不良・JSが動かない）は、 「当日をお楽しみに」の表示に戻るだけで、ページの他の部分は普通に動きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="28">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A43:D43"/>
@@ -2675,6 +2864,8 @@
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A51:D51"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="A25:D25"/>
@@ -2683,7 +2874,10 @@
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -2099,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2360,130 +2360,167 @@
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>メニューやボタンが出ない</t>
+          <t>「承認が必要です」と出る</t>
         </is>
       </c>
       <c r="B51" s="20" t="n"/>
       <c r="C51" s="20" t="n"/>
       <c r="D51" s="20" t="n"/>
     </row>
-    <row r="53" ht="34" customHeight="1">
+    <row r="53" ht="19" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>スマホのアプリでは、メニューも図形ボタンも表示されません。 「実行」列のチェックボックス（章6-3）を使ってください。</t>
+          <t>初回だけ出ます。異常ではありません。 手順は章6-3の「承認のしかた」を見てください。</t>
         </is>
       </c>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
         <is>
+          <t>途中の「このアプリは Google で確認されていません」でつまずきやすいので、 「詳細」→「（安全ではないページ）に移動」 と進んでください。 求められる権限は「このスプレッドシートの表示と編集」だけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>！ 承認を通したくない場合は、「実行」列のチェックボックスを使ってください。 そちらは承認なしで動きます（章6-3）。</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>メニューやボタンが出ない</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="n"/>
+      <c r="C59" s="20" t="n"/>
+      <c r="D59" s="20" t="n"/>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>スマホのアプリでは、メニューも図形ボタンも表示されません。 「実行」列のチェックボックス（章6-3）を使ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
           <t>パソコンでメニューが出ないときは、スプレッドシートを開き直してください。 メニューはシートを開いたときに作られます。</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="19" t="inlineStr">
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>「決勝」なのに「優勝」と出ない</t>
         </is>
       </c>
-      <c r="B57" s="20" t="n"/>
-      <c r="C57" s="20" t="n"/>
-      <c r="D57" s="20" t="n"/>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="20" t="n"/>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>シートの「回戦」欄が「決勝」になっているか確かめてください。 自動で作られた最後の回戦は「決勝」になりますが、手で書いた場合は 「1回戦」のままだと優勝表示になりません。</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>「BRACKET:START / BRACKET:END が見つかりません」</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n"/>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-    </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>index.html からマーカーのコメントを消してしまっています。 消してしまった場合は BRACKET セクションの中に、次の2行を戻してください。</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      &lt;!-- BRACKET:START --&gt;
       &lt;!-- BRACKET:END --&gt;</t>
-        </is>
-      </c>
-      <c r="B65" s="18" t="n"/>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
-    </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="19" t="inlineStr">
-        <is>
-          <t>書き換わってほしくないのに上書きされる</t>
-        </is>
-      </c>
-      <c r="B67" s="20" t="n"/>
-      <c r="C67" s="20" t="n"/>
-      <c r="D67" s="20" t="n"/>
-    </row>
-    <row r="69" ht="34" customHeight="1">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>&lt;!-- BRACKET:START --&gt; 〜 &lt;!-- BRACKET:END --&gt; の間は毎回作り直されます。 手で書いた内容は次の実行で消えます。前後の文章（見出しやリード文）は消えません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>とりあえず結果だけ見たい</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="n"/>
-      <c r="C71" s="20" t="n"/>
-      <c r="D71" s="20" t="n"/>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t>python tools/update_bracket.py tournament.json --dry</t>
         </is>
       </c>
       <c r="B73" s="18" t="n"/>
       <c r="C73" s="18" t="n"/>
       <c r="D73" s="18" t="n"/>
     </row>
-    <row r="75" ht="19" customHeight="1">
-      <c r="A75" s="13" t="inlineStr">
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>書き換わってほしくないのに上書きされる</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+    </row>
+    <row r="77" ht="34" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>&lt;!-- BRACKET:START --&gt; 〜 &lt;!-- BRACKET:END --&gt; の間は毎回作り直されます。 手で書いた内容は次の実行で消えます。前後の文章（見出しやリード文）は消えません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>とりあえず結果だけ見たい</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="n"/>
+      <c r="C79" s="20" t="n"/>
+      <c r="D79" s="20" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>python tools/update_bracket.py tournament.json --dry</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="n"/>
+      <c r="C81" s="18" t="n"/>
+      <c r="D81" s="18" t="n"/>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>index.html を書き換えずに、出力される内容だけ確認できます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="39">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A81:D81"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A67:D67"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A83:D83"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A59:D59"/>
@@ -2492,6 +2529,7 @@
     <mergeCell ref="A49:D49"/>
     <mergeCell ref="A51:D51"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A79:D79"/>
     <mergeCell ref="A61:D61"/>
     <mergeCell ref="A69:D69"/>
     <mergeCell ref="A7:D7"/>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2715,141 +2753,182 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>1. スプレッドシートを開く 2. 上のメニューから 拡張機能 → Apps Script 3. 出てきたコードを全部消して、tools/bracket.gs の中身を貼り付ける 4. 保存（フロッピーのアイコン） 5. スプレッドシートを開き直す → 上に 「ポカジャン大会」というメニューが増えます 6. 「ポカジャン大会 → 次の回戦を作る」を一度押す → 初回だけ許可を求められます。 自分のアカウントで承認してください</t>
+          <t>1. スプレッドシートを開く 2. 上のメニューから 拡張機能 → Apps Script 3. 出てきたコードを全部消して、tools/bracket.gs の中身を貼り付ける 4. 保存（フロッピーのアイコン） 5. スプレッドシートを開き直す → 上に 「ポカジャン大会」というメニューが増えます 6. 「ポカジャン大会 → 次の回戦を作る」を一度押す → 初回だけ承認を求められます（次の「承認のしかた」へ）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>メニューだけで足りるならここまでで完了です。 押しやすくしたい場合は、 次のどちらかを足してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="13" t="inlineStr"/>
-    </row>
-    <row r="29" ht="34" customHeight="1">
+      <c r="A25" s="13" t="inlineStr"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>途中で警告の画面が出ますが、異常ではありません。 自分で貼り付けたスクリプトが Googleの審査を受けていないだけで、中身はこの bracket.gs そのものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="49" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>1. 挿入 → 図形描画 → 四角を描いて「次の回戦を作る」と書く → 保存して閉じる 2. 置かれた図形の右上の 「⋮」→ スクリプトを割り当て 3. createNextRound と入力して OK</t>
+          <t>1. 「承認が必要です」→ 権限を確認 2. 自分の Google アカウントを選ぶ 3. 「このアプリは Google で確認されていません」 と出る → 左下の 「詳細」 をクリック → 「（プロジェクト名）（安全ではないページ）に移動」 をクリック 4. 求められる権限は「このスプレッドシートの表示と編集」だけです → 許可</t>
         </is>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>以後、その図形を押すだけで動きます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="13" t="inlineStr"/>
-    </row>
-    <row r="35" ht="34" customHeight="1">
+          <t>一度通せば、次からは押すだけで動きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>！ 代わりの人がメニューやボタンを使う場合、その人も同じ承認が必要です。 チェックボックス方式（下記）なら承認は要りません。 当日に代理をお願いする 可能性があるなら、チェックボックスを用意しておくほうが確実です。</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+    </row>
+    <row r="35" ht="19" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>1. 空いている列の1行目に「実行」と書く 2. その下のセルを選んで、挿入 → チェックボックス 3. チェックを入れると走り、自動でチェックが外れます</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>！ スマホのアプリでは、メニューも図形ボタンも出ません。 代わりの人がスマホだけで進める可能性があるなら、 チェックボックスを必ず用意しておいてください。</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>手順 6-4. IDをページに書く</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
+          <t>メニューだけで足りるならここまでで完了です。 押しやすくしたい場合は、 次のどちらかを足してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="13" t="inlineStr"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>1. 挿入 → 図形描画 → 四角を描いて「次の回戦を作る」と書く → 保存して閉じる 2. 置かれた図形の右上の 「⋮」→ スクリプトを割り当て 3. createNextRound と入力して OK</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
+          <t>以後、その図形を押すだけで動きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="13" t="inlineStr"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>1. 空いている列の1行目に「実行」と書く 2. その下のセルを選んで、挿入 → チェックボックス 3. チェックを入れると走り、自動でチェックが外れます</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="49" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>この方法だけは承認が要りません。 セルの編集をきっかけに動く仕組み （シンプルトリガー）は、権限を求めない範囲でだけ動くようGoogleが決めているためです。 このスクリプトは同じシートを読み書きするだけなので、その範囲に収まっています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="49" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>！ スマホのアプリでは、メニューも図形ボタンも出ません。 代わりの人がスマホだけで進める可能性があるなら、 チェックボックスを必ず用意しておいてください。 承認の手間もないので、頼むときの説明が「チェックを入れるだけ」で済みます。</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>手順 6-4. IDをページに書く</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
           <t>スプレッドシートのURLはこの形です。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/【この部分がID】/edit#gid=0</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
-    </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="18" t="n"/>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>index.html の &lt;!-- EDIT: トーナメント表のスプレッドシートID --&gt; を探し、 data-sheet="..." にそのIDを貼ります。シート名を変えている場合は data-sheet-name="シート1" も埋めてください（既定のままなら空でOK）。</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>&lt;div class="bracket" data-sheet="1AbCdEf...XyZ" data-sheet-name=""&gt;</t>
         </is>
       </c>
-      <c r="B47" s="18" t="n"/>
-      <c r="C47" s="18" t="n"/>
-      <c r="D47" s="18" t="n"/>
-    </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>そのあと commit して push すれば準備完了です。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>！ IDが空のあいだは「当日をお楽しみに」が出たままになります。 壊れはしません。</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="10" t="n"/>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="19" t="inlineStr">
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>仕組みについて</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-    </row>
-    <row r="55" ht="49" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="20" t="n"/>
+    </row>
+    <row r="67" ht="49" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>サイトは Google の公開データ機能（gviz）を使ってシートを読んでいます。 Googleのスプレッドシートは Access-Control-Allow-Origin を返さないため、 ふつうの読み込み方（fetch）では取得できません。 実測して確認したうえで、 制限を受けない JSONP という方式にしてあります。</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>読めなかったとき（未設定・非公開・通信不良・JSが動かない）は、 「当日をお楽しみに」の表示に戻るだけで、ページの他の部分は普通に動きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="34">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
@@ -2858,17 +2937,23 @@
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A67:D67"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A49:D49"/>
     <mergeCell ref="A51:D51"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A69:D69"/>
     <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A27:D27"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -2099,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2360,7 +2360,7 @@
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>「承認が必要です」と出る</t>
+          <t>「承認が必要です」と出る／「Google で確認されていません」から先に進めない</t>
         </is>
       </c>
       <c r="B51" s="20" t="n"/>
@@ -2377,135 +2377,142 @@
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>途中の「このアプリは Google で確認されていません」でつまずきやすいので、 「詳細」→「（安全ではないページ）に移動」 と進んでください。 求められる権限は「このスプレッドシートの表示と編集」だけです。</t>
+          <t>「このアプリは Google で確認されていません」の画面では、 左下の小さな「詳細」 → 「（安全ではないページ）に移動」 と進みます （英語表示のときは Advanced → Go to … (unsafe)）。</t>
         </is>
       </c>
     </row>
     <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>！ 承認を通したくない場合は、「実行」列のチェックボックスを使ってください。 そちらは承認なしで動きます（章6-3）。</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>それでも進めない場合は、会社や学校の Google アカウントで 管理者が承認をブロックしている可能性があります。 個人アカウントで開き直すか、 下の方法に切り替えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>！ 承認を通さずに済ませる方法があります。 「実行」列のチェックボックスなら承認は要りません（章6-3）。 メニューもボタンも使わず、これだけで当日の操作は足ります。 承認で行き詰まったら、無理に通さずこちらを使ってください。</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>メニューやボタンが出ない</t>
         </is>
       </c>
-      <c r="B59" s="20" t="n"/>
-      <c r="C59" s="20" t="n"/>
-      <c r="D59" s="20" t="n"/>
-    </row>
-    <row r="61" ht="34" customHeight="1">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>スマホのアプリでは、メニューも図形ボタンも表示されません。 「実行」列のチェックボックス（章6-3）を使ってください。</t>
-        </is>
-      </c>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
     </row>
     <row r="63" ht="34" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
         <is>
+          <t>スマホのアプリでは、メニューも図形ボタンも表示されません。 「実行」列のチェックボックス（章6-3）を使ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
           <t>パソコンでメニューが出ないときは、スプレッドシートを開き直してください。 メニューはシートを開いたときに作られます。</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="19" t="inlineStr">
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>「決勝」なのに「優勝」と出ない</t>
         </is>
       </c>
-      <c r="B65" s="20" t="n"/>
-      <c r="C65" s="20" t="n"/>
-      <c r="D65" s="20" t="n"/>
-    </row>
-    <row r="67" ht="34" customHeight="1">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>シートの「回戦」欄が「決勝」になっているか確かめてください。 自動で作られた最後の回戦は「決勝」になりますが、手で書いた場合は 「1回戦」のままだと優勝表示になりません。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="19" t="inlineStr">
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>「BRACKET:START / BRACKET:END が見つかりません」</t>
         </is>
       </c>
-      <c r="B69" s="20" t="n"/>
-      <c r="C69" s="20" t="n"/>
-      <c r="D69" s="20" t="n"/>
-    </row>
-    <row r="71" ht="34" customHeight="1">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>index.html からマーカーのコメントを消してしまっています。 消してしまった場合は BRACKET セクションの中に、次の2行を戻してください。</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="17" t="inlineStr">
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      &lt;!-- BRACKET:START --&gt;
       &lt;!-- BRACKET:END --&gt;</t>
         </is>
       </c>
-      <c r="B73" s="18" t="n"/>
-      <c r="C73" s="18" t="n"/>
-      <c r="D73" s="18" t="n"/>
-    </row>
-    <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
+      <c r="B75" s="18" t="n"/>
+      <c r="C75" s="18" t="n"/>
+      <c r="D75" s="18" t="n"/>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>書き換わってほしくないのに上書きされる</t>
         </is>
       </c>
-      <c r="B75" s="20" t="n"/>
-      <c r="C75" s="20" t="n"/>
-      <c r="D75" s="20" t="n"/>
-    </row>
-    <row r="77" ht="34" customHeight="1">
-      <c r="A77" s="12" t="inlineStr">
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>&lt;!-- BRACKET:START --&gt; 〜 &lt;!-- BRACKET:END --&gt; の間は毎回作り直されます。 手で書いた内容は次の実行で消えます。前後の文章（見出しやリード文）は消えません。</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="19" t="inlineStr">
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>とりあえず結果だけ見たい</t>
         </is>
       </c>
-      <c r="B79" s="20" t="n"/>
-      <c r="C79" s="20" t="n"/>
-      <c r="D79" s="20" t="n"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="17" t="inlineStr">
+      <c r="B81" s="20" t="n"/>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="20" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json --dry</t>
         </is>
       </c>
-      <c r="B81" s="18" t="n"/>
-      <c r="C81" s="18" t="n"/>
-      <c r="D81" s="18" t="n"/>
-    </row>
-    <row r="83" ht="19" customHeight="1">
-      <c r="A83" s="13" t="inlineStr">
+      <c r="B83" s="18" t="n"/>
+      <c r="C83" s="18" t="n"/>
+      <c r="D83" s="18" t="n"/>
+    </row>
+    <row r="85" ht="19" customHeight="1">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>index.html を書き換えずに、出力される内容だけ確認できます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
@@ -2545,6 +2552,7 @@
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A85:D85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
@@ -2634,7 +2642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2818,117 +2826,138 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="13" t="inlineStr"/>
     </row>
-    <row r="45" ht="34" customHeight="1">
+    <row r="45" ht="19" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>1. 空いている列の1行目に「実行」と書く 2. その下のセルを選んで、挿入 → チェックボックス 3. チェックを入れると走り、自動でチェックが外れます</t>
+          <t>承認でつまずいたときは、これだけ用意すれば足ります。 メニューもボタンも要りません。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="49" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
+          <t>1. 空いている列の1行目に「実行」と入力する （例：A〜Dを使っているなら G1。「実行ボタン」でも構いません） 2. そのすぐ下のセル（例：G2）を選ぶ 3. メニューの 挿入 → チェックボックス 4. 隣のセルに「次の回戦を作る」と書いておくと、当日ほかの人が見て分かります</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>使うときは、その回戦の勝ちを入れ終わってから チェックを入れるだけです。 行が追加され、チェックは自動で外れます（また押せる状態に戻ります）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>まだ入れ終わっていないときにチェックしても、行は増えません。チェックだけ外れます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="49" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
           <t>この方法だけは承認が要りません。 セルの編集をきっかけに動く仕組み （シンプルトリガー）は、権限を求めない範囲でだけ動くようGoogleが決めているためです。 このスクリプトは同じシートを読み書きするだけなので、その範囲に収まっています。</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="49" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
+    <row r="55" ht="49" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>！ スマホのアプリでは、メニューも図形ボタンも出ません。 代わりの人がスマホだけで進める可能性があるなら、 チェックボックスを必ず用意しておいてください。 承認の手間もないので、頼むときの説明が「チェックを入れるだけ」で済みます。</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>手順 6-4. IDをページに書く</t>
         </is>
       </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>スプレッドシートのURLはこの形です。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/【この部分がID】/edit#gid=0</t>
         </is>
       </c>
-      <c r="B55" s="18" t="n"/>
-      <c r="C55" s="18" t="n"/>
-      <c r="D55" s="18" t="n"/>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>index.html の &lt;!-- EDIT: トーナメント表のスプレッドシートID --&gt; を探し、 data-sheet="..." にそのIDを貼ります。シート名を変えている場合は data-sheet-name="シート1" も埋めてください（既定のままなら空でOK）。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="17" t="inlineStr">
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>&lt;div class="bracket" data-sheet="1AbCdEf...XyZ" data-sheet-name=""&gt;</t>
         </is>
       </c>
-      <c r="B59" s="18" t="n"/>
-      <c r="C59" s="18" t="n"/>
-      <c r="D59" s="18" t="n"/>
-    </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+    </row>
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>そのあと commit して push すれば準備完了です。</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="14" t="inlineStr">
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>！ IDが空のあいだは「当日をお楽しみに」が出たままになります。 壊れはしません。</t>
         </is>
       </c>
-      <c r="B63" s="10" t="n"/>
-      <c r="C63" s="10" t="n"/>
-      <c r="D63" s="10" t="n"/>
-    </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="19" t="inlineStr">
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>仕組みについて</t>
         </is>
       </c>
-      <c r="B65" s="20" t="n"/>
-      <c r="C65" s="20" t="n"/>
-      <c r="D65" s="20" t="n"/>
-    </row>
-    <row r="67" ht="49" customHeight="1">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+    </row>
+    <row r="73" ht="49" customHeight="1">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t>サイトは Google の公開データ機能（gviz）を使ってシートを読んでいます。 Googleのスプレッドシートは Access-Control-Allow-Origin を返さないため、 ふつうの読み込み方（fetch）では取得できません。 実測して確認したうえで、 制限を受けない JSONP という方式にしてあります。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="34" customHeight="1">
-      <c r="A69" s="12" t="inlineStr">
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>読めなかったとき（未設定・非公開・通信不良・JSが動かない）は、 「当日をお楽しみに」の表示に戻るだけで、ページの他の部分は普通に動きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="37">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
@@ -2945,6 +2974,7 @@
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A73:D73"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A49:D49"/>
     <mergeCell ref="A51:D51"/>
@@ -2956,12 +2986,14 @@
     <mergeCell ref="A65:D65"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A75:D75"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A71:D71"/>
     <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -1472,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1726,267 +1726,277 @@
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>！ CPUが上位に入った卓は、その下の順位の人に印を付けてください。 CPUは勝ち上がらないルールなので、繰り上がった人が次へ進みます。 シートの CPU の行に印を付けても、次の回戦には出てきません。</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>・まだ終わっていない卓は空のままにしてください</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>・2回戦以降の行は手で書かなくて大丈夫です。 全部の卓に印を入れたあと、 「次の回戦を作る」を押せば組まれます（下記）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>・メモ用の列を足しても構いません。 見出しの言葉（回戦／卓／参加者／勝ち）で 列を探すので、順番を入れ替えても動きます</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="13" t="inlineStr"/>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="13" t="inlineStr"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>その回戦の勝ちを入れ終わったら、「次の回戦を作る」を押してください。 次の回戦の行がシートに追加されます（薄い黄色で色が付きます）。</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>押しかたは3つあります。どれも同じことをします（章6-3で用意します）。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="15" t="inlineStr"/>
-      <c r="B41" s="15" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="15" t="inlineStr"/>
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>押しかた</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>使える場所</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>メニューの「ポカジャン大会 → 次の回戦を作る」</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>パソコン</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>シートに置いた図形ボタン</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>パソコン</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>「実行」列のチェックボックス</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>スマホでも押せます</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>勝手には増えません。 押したときだけ動くので、入力の途中で組まれる心配はありません。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
+          <t>勝手には増えません。 押したときだけ動くので、入力の途中で組まれる心配はありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
           <t>作れないときは、画面の右下に理由が出ます。</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>1回戦の勝ちの数がそろっていません（卓1は2人・卓2は2人・卓3は1人）。入れ忘れがないか確かめてください。</t>
         </is>
       </c>
-      <c r="B50" s="18" t="n"/>
-      <c r="C50" s="18" t="n"/>
-      <c r="D50" s="18" t="n"/>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="18" t="n"/>
+      <c r="D52" s="18" t="n"/>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>作れる条件は、いちばん下の回戦について次の3つです。</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>1. 卓が2つ以上ある（1つなら、それが最後の卓です） 2. すべての卓に勝ちの印が付いている 3. 卓ごとの勝ちの数がそろっている（卓1が2人なら、卓2も卓3も2人）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>追加された行の「勝ち」に、また印を入れてください。これを決勝まで繰り返すだけです。</t>
         </is>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
         <is>
+          <t>追加された行の「勝ち」に、また印を入れてください。これを決勝まで繰り返すだけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
           <t>勝った人は順番に振り分けるので、同じ卓から上がった人どうしが固まりません。</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="46" customHeight="1">
-      <c r="A60" s="17" t="inlineStr">
+    <row r="62" ht="46" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>1回戦  卓1 → A, B が勝ち上がり        2回戦  卓1 = A, C, E
        卓2 → C, D                            卓2 = B, D, F
        卓3 → E, F                     （出身の卓がばらけます）</t>
         </is>
       </c>
-      <c r="B60" s="18" t="n"/>
-      <c r="C60" s="18" t="n"/>
-      <c r="D60" s="18" t="n"/>
-    </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="n"/>
+    </row>
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>ただし抽選ではなく決まった順序です。同じ勝ち上がりなら毎回同じ組み合わせになります。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>組み合わせを手で決めたいときは、追加された行を書き換えてかまいません。 一度作られた行が勝手に作り直されることはありません。</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="19" t="inlineStr">
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>手順 2-3. サイトを開き直す</t>
         </is>
       </c>
-      <c r="B66" s="20" t="n"/>
-      <c r="C66" s="20" t="n"/>
-      <c r="D66" s="20" t="n"/>
-    </row>
-    <row r="68" ht="34" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+    </row>
+    <row r="70" ht="34" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>それだけです。 ページを開くたびにスプレッドシートを読みに行くので、 git も python も要りません。反映まで数十秒かかることがあります。</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="19" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
+    <row r="72" ht="19" customHeight="1">
+      <c r="A72" s="12" t="inlineStr">
         <is>
           <t>2回戦以降も 2-2 の繰り返しです。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="19" t="inlineStr">
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>手順 2-4. 決勝</t>
         </is>
       </c>
-      <c r="B72" s="20" t="n"/>
-      <c r="C72" s="20" t="n"/>
-      <c r="D72" s="20" t="n"/>
-    </row>
-    <row r="74" ht="34" customHeight="1">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="B74" s="20" t="n"/>
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="20" t="n"/>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="A76" s="12" t="inlineStr">
         <is>
           <t>残りが4人以下になると、「次の回戦を作る」を押したときに決勝の行ができます。 優勝者1名にだけ○を入れてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="34" customHeight="1">
-      <c r="A76" s="14" t="inlineStr">
+    <row r="78" ht="34" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
         <is>
           <t>！ 見出しが「決勝」の回戦だけ「優勝」が出ます。参加者が4人以下で 1回戦がそのまま決勝になる場合は、シートの「回戦」欄に「決勝」と書いてください。</t>
         </is>
       </c>
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="10" t="n"/>
-    </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="19" t="inlineStr">
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>（任意）最終結果をページに焼き付ける</t>
         </is>
       </c>
-      <c r="B78" s="20" t="n"/>
-      <c r="C78" s="20" t="n"/>
-      <c r="D78" s="20" t="n"/>
-    </row>
-    <row r="80" ht="34" customHeight="1">
-      <c r="A80" s="12" t="inlineStr">
+      <c r="B80" s="20" t="n"/>
+      <c r="C80" s="20" t="n"/>
+      <c r="D80" s="20" t="n"/>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" s="12" t="inlineStr">
         <is>
           <t>大会が終わったあと、スプレッドシートを消しても表が残るようにしたいときだけ、 主催者のパソコンで次を実行します。当日は不要です。</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="17" t="inlineStr">
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json
 git add -A &amp;&amp; git commit -m "最終結果" &amp;&amp; git push</t>
         </is>
       </c>
-      <c r="B82" s="18" t="n"/>
-      <c r="C82" s="18" t="n"/>
-      <c r="D82" s="18" t="n"/>
+      <c r="B84" s="18" t="n"/>
+      <c r="C84" s="18" t="n"/>
+      <c r="D84" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A35:D35"/>
@@ -1998,6 +2008,7 @@
     <mergeCell ref="A68:D68"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
@@ -2010,7 +2021,8 @@
     <mergeCell ref="A78:D78"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A84:D84"/>
     <mergeCell ref="A66:D66"/>
     <mergeCell ref="A80:D80"/>
     <mergeCell ref="A37:D37"/>
@@ -2019,9 +2031,8 @@
     <mergeCell ref="A74:D74"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A76:D76"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -1472,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1855,7 +1855,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>1回戦の勝ちの数がそろっていません（卓1は2人・卓2は2人・卓3は1人）。入れ忘れがないか確かめてください。</t>
+          <t>1回戦の 卓2 に、まだ勝ちの印がありません。</t>
         </is>
       </c>
       <c r="B52" s="18" t="n"/>
@@ -1865,138 +1865,169 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>作れる条件は、いちばん下の回戦について次の3つです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="34" customHeight="1">
+          <t>作れる条件は、いちばん下の回戦について次の2つです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>1. 卓が2つ以上ある（1つなら、それが最後の卓です） 2. すべての卓に勝ちの印が付いている 3. 卓ごとの勝ちの数がそろっている（卓1が2人なら、卓2も卓3も2人）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="19" customHeight="1">
+          <t>1. 卓が2つ以上ある（1つなら、それが最後の卓です） 2. すべての卓に、勝ちの印が1人以上ある</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="34" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>追加された行の「勝ち」に、また印を入れてください。これを決勝まで繰り返すだけです。</t>
+          <t>勝ち上がる人数は卓ごとに違ってかまいません。 参加人数によって変わるためです。 「卓1からは2人、卓2からは1人」でもそのまま組めます。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="12" t="inlineStr">
         <is>
+          <t>ただし数が違うときは、入れ忘れの可能性もあるのでひとこと添えて知らせます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>2回戦を作りました（5人／2卓）。　※卓ごとの勝ちの数が違いました（卓1は2人・卓2は1人・卓3は2人）。入れ忘れでなければそのままで大丈夫です。</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="n"/>
+    </row>
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>止めはしません。 意図してそうしているならそのまま進めてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>追加された行の「勝ち」に、また印を入れてください。これを決勝まで繰り返すだけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
           <t>勝った人は順番に振り分けるので、同じ卓から上がった人どうしが固まりません。</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="46" customHeight="1">
-      <c r="A62" s="17" t="inlineStr">
+    <row r="70" ht="46" customHeight="1">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t>1回戦  卓1 → A, B が勝ち上がり        2回戦  卓1 = A, C, E
        卓2 → C, D                            卓2 = B, D, F
        卓3 → E, F                     （出身の卓がばらけます）</t>
         </is>
       </c>
-      <c r="B62" s="18" t="n"/>
-      <c r="C62" s="18" t="n"/>
-      <c r="D62" s="18" t="n"/>
-    </row>
-    <row r="64" ht="19" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t>ただし抽選ではなく決まった順序です。同じ勝ち上がりなら毎回同じ組み合わせになります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="34" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>組み合わせを手で決めたいときは、追加された行を書き換えてかまいません。 一度作られた行が勝手に作り直されることはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="19" t="inlineStr">
-        <is>
-          <t>手順 2-3. サイトを開き直す</t>
-        </is>
-      </c>
-      <c r="B68" s="20" t="n"/>
-      <c r="C68" s="20" t="n"/>
-      <c r="D68" s="20" t="n"/>
-    </row>
-    <row r="70" ht="34" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>それだけです。 ページを開くたびにスプレッドシートを読みに行くので、 git も python も要りません。反映まで数十秒かかることがあります。</t>
-        </is>
-      </c>
+      <c r="B70" s="18" t="n"/>
+      <c r="C70" s="18" t="n"/>
+      <c r="D70" s="18" t="n"/>
     </row>
     <row r="72" ht="19" customHeight="1">
       <c r="A72" s="12" t="inlineStr">
         <is>
+          <t>ただし抽選ではなく決まった順序です。同じ勝ち上がりなら毎回同じ組み合わせになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>組み合わせを手で決めたいときは、追加された行を書き換えてかまいません。 一度作られた行が勝手に作り直されることはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>手順 2-3. サイトを開き直す</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="n"/>
+      <c r="C76" s="20" t="n"/>
+      <c r="D76" s="20" t="n"/>
+    </row>
+    <row r="78" ht="34" customHeight="1">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>それだけです。 ページを開くたびにスプレッドシートを読みに行くので、 git も python も要りません。反映まで数十秒かかることがあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="19" customHeight="1">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
           <t>2回戦以降も 2-2 の繰り返しです。</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="19" t="inlineStr">
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>手順 2-4. 決勝</t>
         </is>
       </c>
-      <c r="B74" s="20" t="n"/>
-      <c r="C74" s="20" t="n"/>
-      <c r="D74" s="20" t="n"/>
-    </row>
-    <row r="76" ht="34" customHeight="1">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="B82" s="20" t="n"/>
+      <c r="C82" s="20" t="n"/>
+      <c r="D82" s="20" t="n"/>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="12" t="inlineStr">
         <is>
           <t>残りが4人以下になると、「次の回戦を作る」を押したときに決勝の行ができます。 優勝者1名にだけ○を入れてください。 そこだけ濃い金色で「優勝」と表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="34" customHeight="1">
-      <c r="A78" s="14" t="inlineStr">
+    <row r="86" ht="34" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
         <is>
           <t>！ 見出しが「決勝」の回戦だけ「優勝」が出ます。参加者が4人以下で 1回戦がそのまま決勝になる場合は、シートの「回戦」欄に「決勝」と書いてください。</t>
         </is>
       </c>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="10" t="n"/>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="19" t="inlineStr">
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="10" t="n"/>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="19" t="inlineStr">
         <is>
           <t>（任意）最終結果をページに焼き付ける</t>
         </is>
       </c>
-      <c r="B80" s="20" t="n"/>
-      <c r="C80" s="20" t="n"/>
-      <c r="D80" s="20" t="n"/>
-    </row>
-    <row r="82" ht="34" customHeight="1">
-      <c r="A82" s="12" t="inlineStr">
+      <c r="B88" s="20" t="n"/>
+      <c r="C88" s="20" t="n"/>
+      <c r="D88" s="20" t="n"/>
+    </row>
+    <row r="90" ht="34" customHeight="1">
+      <c r="A90" s="12" t="inlineStr">
         <is>
           <t>大会が終わったあと、スプレッドシートを消しても表が残るようにしたいときだけ、 主催者のパソコンで次を実行します。当日は不要です。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="17" t="inlineStr">
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json
 git add -A &amp;&amp; git commit -m "最終結果" &amp;&amp; git push</t>
         </is>
       </c>
-      <c r="B84" s="18" t="n"/>
-      <c r="C84" s="18" t="n"/>
-      <c r="D84" s="18" t="n"/>
+      <c r="B92" s="18" t="n"/>
+      <c r="C92" s="18" t="n"/>
+      <c r="D92" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="40">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A35:D35"/>
@@ -2010,6 +2041,7 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A92:D92"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A64:D64"/>
@@ -2018,11 +2050,13 @@
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A88:D88"/>
     <mergeCell ref="A78:D78"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A90:D90"/>
     <mergeCell ref="A66:D66"/>
     <mergeCell ref="A80:D80"/>
     <mergeCell ref="A37:D37"/>
@@ -2031,6 +2065,7 @@
     <mergeCell ref="A74:D74"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A86:D86"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A76:D76"/>
   </mergeCells>
@@ -2110,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2328,242 +2363,241 @@
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>「勝ちの数がそろっていません（卓1は2人・卓2は1人…）」</t>
+          <t>「〜は1卓だけなので、これが最後です」</t>
         </is>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>入れ忘れです。数をそろえてください</t>
+          <t>もう決勝まで来ています。正常です</t>
         </is>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>「〜は1卓だけなので、これが最後です」</t>
+          <t>「シートの見出しが読めません」</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>もう決勝まで来ています。正常です</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>「シートの見出しが読めません」</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
           <t>1行目を「回戦 / 卓 / 参加者 / 勝ち」にしてください</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>！ 「※卓ごとの勝ちの数が違いました」は注意書きであって失敗ではありません。 行はもう作られています。入れ忘れでなければそのまま進めてください。</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>何も出ない場合は、スクリプトが入っていないか承認がまだです。 拡張機能 → Apps Script を開き、コードが貼られているか確認してください。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>「承認が必要です」と出る／「Google で確認されていません」から先に進めない</t>
         </is>
       </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>初回だけ出ます。異常ではありません。 手順は章6-3の「承認のしかた」を見てください。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>「このアプリは Google で確認されていません」の画面では、 左下の小さな「詳細」 → 「（安全ではないページ）に移動」 と進みます （英語表示のときは Advanced → Go to … (unsafe)）。</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>それでも進めない場合は、会社や学校の Google アカウントで 管理者が承認をブロックしている可能性があります。 個人アカウントで開き直すか、 下の方法に切り替えてください。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>！ 承認を通さずに済ませる方法があります。 「実行」列のチェックボックスなら承認は要りません（章6-3）。 メニューもボタンも使わず、これだけで当日の操作は足ります。 承認で行き詰まったら、無理に通さずこちらを使ってください。</t>
         </is>
       </c>
-      <c r="B59" s="10" t="n"/>
-      <c r="C59" s="10" t="n"/>
-      <c r="D59" s="10" t="n"/>
-    </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>メニューやボタンが出ない</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n"/>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-    </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="B62" s="20" t="n"/>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="20" t="n"/>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>スマホのアプリでは、メニューも図形ボタンも表示されません。 「実行」列のチェックボックス（章6-3）を使ってください。</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>パソコンでメニューが出ないときは、スプレッドシートを開き直してください。 メニューはシートを開いたときに作られます。</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="19" t="inlineStr">
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>「決勝」なのに「優勝」と出ない</t>
         </is>
       </c>
-      <c r="B67" s="20" t="n"/>
-      <c r="C67" s="20" t="n"/>
-      <c r="D67" s="20" t="n"/>
-    </row>
-    <row r="69" ht="34" customHeight="1">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+    </row>
+    <row r="70" ht="34" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>シートの「回戦」欄が「決勝」になっているか確かめてください。 自動で作られた最後の回戦は「決勝」になりますが、手で書いた場合は 「1回戦」のままだと優勝表示になりません。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>「BRACKET:START / BRACKET:END が見つかりません」</t>
         </is>
       </c>
-      <c r="B71" s="20" t="n"/>
-      <c r="C71" s="20" t="n"/>
-      <c r="D71" s="20" t="n"/>
-    </row>
-    <row r="73" ht="34" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
+      <c r="B72" s="20" t="n"/>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="20" t="n"/>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="13" t="inlineStr">
         <is>
           <t>index.html からマーカーのコメントを消してしまっています。 消してしまった場合は BRACKET セクションの中に、次の2行を戻してください。</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="17" t="inlineStr">
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      &lt;!-- BRACKET:START --&gt;
       &lt;!-- BRACKET:END --&gt;</t>
         </is>
       </c>
-      <c r="B75" s="18" t="n"/>
-      <c r="C75" s="18" t="n"/>
-      <c r="D75" s="18" t="n"/>
-    </row>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="19" t="inlineStr">
+      <c r="B76" s="18" t="n"/>
+      <c r="C76" s="18" t="n"/>
+      <c r="D76" s="18" t="n"/>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>書き換わってほしくないのに上書きされる</t>
         </is>
       </c>
-      <c r="B77" s="20" t="n"/>
-      <c r="C77" s="20" t="n"/>
-      <c r="D77" s="20" t="n"/>
-    </row>
-    <row r="79" ht="34" customHeight="1">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="20" t="n"/>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t>&lt;!-- BRACKET:START --&gt; 〜 &lt;!-- BRACKET:END --&gt; の間は毎回作り直されます。 手で書いた内容は次の実行で消えます。前後の文章（見出しやリード文）は消えません。</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="19" t="inlineStr">
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>とりあえず結果だけ見たい</t>
         </is>
       </c>
-      <c r="B81" s="20" t="n"/>
-      <c r="C81" s="20" t="n"/>
-      <c r="D81" s="20" t="n"/>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="B82" s="20" t="n"/>
+      <c r="C82" s="20" t="n"/>
+      <c r="D82" s="20" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json --dry</t>
         </is>
       </c>
-      <c r="B83" s="18" t="n"/>
-      <c r="C83" s="18" t="n"/>
-      <c r="D83" s="18" t="n"/>
-    </row>
-    <row r="85" ht="19" customHeight="1">
-      <c r="A85" s="13" t="inlineStr">
+      <c r="B84" s="18" t="n"/>
+      <c r="C84" s="18" t="n"/>
+      <c r="D84" s="18" t="n"/>
+    </row>
+    <row r="86" ht="19" customHeight="1">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>index.html を書き換えずに、出力される内容だけ確認できます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="41">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A68:D68"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A67:D67"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A82:D82"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A80:D80"/>
     <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A86:D86"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/docs/大会運営ガイド.xlsx
+++ b/docs/大会運営ガイド.xlsx
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -923,24 +923,54 @@
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>結果スクショの送り先を決めて、参加者に伝える用意ができている（章2-5）</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>スプレッドシートに「得点」のメモ列を足してある（任意・章2-5）</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>！ 当日にパソコンは要りません。 更新はスプレッドシートの「勝ち」に印を入れるだけで、 git も python も使いません。前日の抽選（章1）だけパソコンで行います。</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -1472,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2001,37 +2031,108 @@
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>（任意）最終結果をページに焼き付ける</t>
+          <t>手順 2-5. 結果スクショを集めて最高得点者を出す</t>
         </is>
       </c>
       <c r="B88" s="20" t="n"/>
       <c r="C88" s="20" t="n"/>
       <c r="D88" s="20" t="n"/>
     </row>
-    <row r="90" ht="34" customHeight="1">
+    <row r="90" ht="19" customHeight="1">
       <c r="A90" s="12" t="inlineStr">
         <is>
+          <t>勝ち上がりの管理とは別に、点数の集計が要ります。 表彰の「最高得点者」を決めるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="34" customHeight="1">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>！ 結果画面は数秒で自動的に切り替わります。 撮り逃しは起きる前提で構えてください。 参加者には「同卓の1人ぶんで十分」「撮り逃したら自己申告」と案内してあります （サイトの RULE「最高得点者」と FLOW 04）。</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="10" t="n"/>
+    </row>
+    <row r="94" ht="19" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>・送り先を先に決めて、卓分けの案内と一緒に伝えてください。 主催者のDMでも、 専用チャンネルでもかまいません</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="19" customHeight="1">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>・必要なのは卓ごとに1枚です。届いていない卓は、その卓のVCで声をかけてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="19" customHeight="1">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>・撮り逃した卓は、点数の自己申告を集めてください。 同卓の人の申告と食い違ったら、 その卓の4人に確認します</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="19" customHeight="1">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>・CPUは表彰の対象外です。 CPUの点数がいちばん高くても、人のなかの最高点を取ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="34" customHeight="1">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>記録はスプレッドシートに「得点」の列を足すのが手軽です。見出しの言葉 （回戦／卓／参加者／勝ち）で列を探すので、列を足してもトーナメント表の表示には 影響しません（手順2-2）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="34" customHeight="1">
+      <c r="A101" s="13" t="inlineStr">
+        <is>
+          <t>全部の卓ぶん集まったら、いちばん高い点数を出した人が最高得点者です。 結果発表で読み上げてください（サイトの FLOW 06）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>（任意）最終結果をページに焼き付ける</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="20" t="n"/>
+    </row>
+    <row r="105" ht="34" customHeight="1">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
           <t>大会が終わったあと、スプレッドシートを消しても表が残るようにしたいときだけ、 主催者のパソコンで次を実行します。当日は不要です。</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="32" customHeight="1">
-      <c r="A92" s="17" t="inlineStr">
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="17" t="inlineStr">
         <is>
           <t>python tools/update_bracket.py tournament.json
 git add -A &amp;&amp; git commit -m "最終結果" &amp;&amp; git push</t>
         </is>
       </c>
-      <c r="B92" s="18" t="n"/>
-      <c r="C92" s="18" t="n"/>
-      <c r="D92" s="18" t="n"/>
+      <c r="B107" s="18" t="n"/>
+      <c r="C107" s="18" t="n"/>
+      <c r="D107" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="49">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A97:D97"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A96:D96"/>
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A52:D52"/>
@@ -2047,14 +2148,18 @@
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="A82:D82"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A107:D107"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A94:D94"/>
     <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A103:D103"/>
     <mergeCell ref="A88:D88"/>
     <mergeCell ref="A78:D78"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A99:D99"/>
     <mergeCell ref="A84:D84"/>
     <mergeCell ref="A90:D90"/>
     <mergeCell ref="A66:D66"/>
@@ -2063,9 +2168,12 @@
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A105:D105"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A101:D101"/>
     <mergeCell ref="A86:D86"/>
+    <mergeCell ref="A95:D95"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A76:D76"/>
   </mergeCells>
